--- a/excel_reports/backtest_compare/s9/compare_s9_M15_20260528_0800_20260608_1000.xlsx
+++ b/excel_reports/backtest_compare/s9/compare_s9_M15_20260528_0800_20260608_1000.xlsx
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Live Only'!$A$1:$BK$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Backtest Only'!$A$1:$BK$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Matches'!$A$1:$BK$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-09 20:45:56</t>
+          <t>2026-06-18 17:12:20</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
     <col width="20" customWidth="1" min="37" max="37"/>
     <col width="20" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
-    <col width="11" customWidth="1" min="40" max="40"/>
+    <col width="16" customWidth="1" min="40" max="40"/>
     <col width="15" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="15" customWidth="1" min="43" max="43"/>
@@ -1288,10 +1288,10 @@
         <v>46176.85416666666</v>
       </c>
       <c r="AE3" s="9" t="n">
-        <v>46177.28125</v>
+        <v>46176.85416666666</v>
       </c>
       <c r="AF3" s="8" t="n">
-        <v>4463.98</v>
+        <v>4435.1</v>
       </c>
       <c r="AG3" s="8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>4440.17</v>
       </c>
       <c r="AI3" s="8" t="n">
-        <v>23.81</v>
+        <v>-5.07</v>
       </c>
       <c r="AJ3" s="8" t="inlineStr"/>
       <c r="AK3" s="8" t="inlineStr"/>
@@ -1310,7 +1310,7 @@
       <c r="AM3" s="8" t="inlineStr"/>
       <c r="AN3" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL_GUARD_GROUP</t>
         </is>
       </c>
       <c r="AO3" s="8" t="inlineStr"/>
@@ -1324,8 +1324,16 @@
       <c r="AW3" s="8" t="inlineStr"/>
       <c r="AX3" s="8" t="inlineStr"/>
       <c r="AY3" s="8" t="inlineStr"/>
-      <c r="AZ3" s="8" t="inlineStr"/>
-      <c r="BA3" s="8" t="inlineStr"/>
+      <c r="AZ3" s="8" t="inlineStr">
+        <is>
+          <t>M15+M30+H1</t>
+        </is>
+      </c>
+      <c r="BA3" s="8" t="inlineStr">
+        <is>
+          <t>M30</t>
+        </is>
+      </c>
       <c r="BB3" s="8" t="inlineStr"/>
       <c r="BC3" s="8" t="inlineStr"/>
       <c r="BD3" s="8" t="inlineStr"/>
@@ -2679,7 +2687,7 @@
     <col width="20" customWidth="1" min="37" max="37"/>
     <col width="20" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
-    <col width="11" customWidth="1" min="40" max="40"/>
+    <col width="16" customWidth="1" min="40" max="40"/>
     <col width="15" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="15" customWidth="1" min="43" max="43"/>
@@ -3155,10 +3163,10 @@
         <v>46176.85416666666</v>
       </c>
       <c r="AE3" s="9" t="n">
-        <v>46177.28125</v>
+        <v>46176.85416666666</v>
       </c>
       <c r="AF3" s="8" t="n">
-        <v>4463.98</v>
+        <v>4435.1</v>
       </c>
       <c r="AG3" s="8" t="inlineStr">
         <is>
@@ -3169,7 +3177,7 @@
         <v>4440.17</v>
       </c>
       <c r="AI3" s="8" t="n">
-        <v>23.81</v>
+        <v>-5.07</v>
       </c>
       <c r="AJ3" s="8" t="inlineStr"/>
       <c r="AK3" s="8" t="inlineStr"/>
@@ -3177,7 +3185,7 @@
       <c r="AM3" s="8" t="inlineStr"/>
       <c r="AN3" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL_GUARD_GROUP</t>
         </is>
       </c>
       <c r="AO3" s="8" t="inlineStr"/>
@@ -3191,8 +3199,16 @@
       <c r="AW3" s="8" t="inlineStr"/>
       <c r="AX3" s="8" t="inlineStr"/>
       <c r="AY3" s="8" t="inlineStr"/>
-      <c r="AZ3" s="8" t="inlineStr"/>
-      <c r="BA3" s="8" t="inlineStr"/>
+      <c r="AZ3" s="8" t="inlineStr">
+        <is>
+          <t>M15+M30+H1</t>
+        </is>
+      </c>
+      <c r="BA3" s="8" t="inlineStr">
+        <is>
+          <t>M30</t>
+        </is>
+      </c>
       <c r="BB3" s="8" t="inlineStr"/>
       <c r="BC3" s="8" t="inlineStr"/>
       <c r="BD3" s="8" t="inlineStr"/>
@@ -4042,7 +4058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4099,7 +4115,7 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
@@ -4108,16 +4124,16 @@
         </is>
       </c>
       <c r="D2" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>86.98999999999999</v>
+        <v>-39.2</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>46176.85416666666</v>
+        <v>46176.25</v>
       </c>
       <c r="G2" s="11" t="n">
-        <v>46179.125</v>
+        <v>46179.04166666666</v>
       </c>
     </row>
     <row r="3">
@@ -4128,7 +4144,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
@@ -4140,13 +4156,13 @@
         <v>2</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>-39.2</v>
+        <v>63.18</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>46176.25</v>
+        <v>46177.21875</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>46179.04166666666</v>
+        <v>46179.125</v>
       </c>
     </row>
     <row r="4">
@@ -4181,12 +4197,12 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>bt_gap</t>
+          <t>bt</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>NO_SAME_SIDE_CANDIDATE</t>
+          <t>SL_GUARD_GROUP</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -4195,27 +4211,27 @@
         </is>
       </c>
       <c r="D5" s="10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>31.11</v>
+        <v>-5.07</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>46176.25</v>
+        <v>46176.85416666666</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>46179.125</v>
+        <v>46176.85416666666</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>bt_s14_family</t>
+          <t>bt_gap</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>NO_SAME_SIDE_CANDIDATE</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -4224,10 +4240,10 @@
         </is>
       </c>
       <c r="D6" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>47.79</v>
+        <v>2.23</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>46176.25</v>
@@ -4249,24 +4265,53 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>46176.25</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>46179.125</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>bt_s14_family</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D8" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E8" s="10" t="n">
         <v>-16.68</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F8" s="11" t="n">
         <v>46177.76041666666</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G8" s="11" t="n">
         <v>46177.76041666666</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7"/>
+  <autoFilter ref="A1:G8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/excel_reports/backtest_compare/s9/compare_s9_M15_20260528_0800_20260608_1000.xlsx
+++ b/excel_reports/backtest_compare/s9/compare_s9_M15_20260528_0800_20260608_1000.xlsx
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Live Only'!$A$1:$BK$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Backtest Only'!$A$1:$BK$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Matches'!$A$1:$BK$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-18 17:12:20</t>
+          <t>2026-06-19 09:02:59</t>
         </is>
       </c>
     </row>
@@ -1569,10 +1569,10 @@
         <v>46179.04166666666</v>
       </c>
       <c r="AE6" s="9" t="n">
-        <v>46181.52083333334</v>
+        <v>46179.08333333334</v>
       </c>
       <c r="AF6" s="8" t="n">
-        <v>4298.57</v>
+        <v>4325.11</v>
       </c>
       <c r="AG6" s="8" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>4323.43</v>
       </c>
       <c r="AI6" s="8" t="n">
-        <v>-24.86</v>
+        <v>1.68</v>
       </c>
       <c r="AJ6" s="8" t="inlineStr"/>
       <c r="AK6" s="8" t="inlineStr"/>
@@ -1600,11 +1600,23 @@
       <c r="AR6" s="8" t="inlineStr"/>
       <c r="AS6" s="8" t="inlineStr"/>
       <c r="AT6" s="8" t="inlineStr"/>
-      <c r="AU6" s="8" t="inlineStr"/>
-      <c r="AV6" s="8" t="inlineStr"/>
-      <c r="AW6" s="8" t="inlineStr"/>
-      <c r="AX6" s="8" t="inlineStr"/>
-      <c r="AY6" s="8" t="inlineStr"/>
+      <c r="AU6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV6" s="8" t="n"/>
+      <c r="AW6" s="8" t="n">
+        <v>4325.11</v>
+      </c>
+      <c r="AX6" s="8" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="AY6" s="8" t="inlineStr">
+        <is>
+          <t>M1 4325.11</t>
+        </is>
+      </c>
       <c r="AZ6" s="8" t="inlineStr"/>
       <c r="BA6" s="8" t="inlineStr"/>
       <c r="BB6" s="8" t="inlineStr"/>
@@ -3444,10 +3456,10 @@
         <v>46179.04166666666</v>
       </c>
       <c r="AE6" s="9" t="n">
-        <v>46181.52083333334</v>
+        <v>46179.08333333334</v>
       </c>
       <c r="AF6" s="8" t="n">
-        <v>4298.57</v>
+        <v>4325.11</v>
       </c>
       <c r="AG6" s="8" t="inlineStr">
         <is>
@@ -3458,7 +3470,7 @@
         <v>4323.43</v>
       </c>
       <c r="AI6" s="8" t="n">
-        <v>-24.86</v>
+        <v>1.68</v>
       </c>
       <c r="AJ6" s="8" t="inlineStr"/>
       <c r="AK6" s="8" t="inlineStr"/>
@@ -3475,11 +3487,23 @@
       <c r="AR6" s="8" t="inlineStr"/>
       <c r="AS6" s="8" t="inlineStr"/>
       <c r="AT6" s="8" t="inlineStr"/>
-      <c r="AU6" s="8" t="inlineStr"/>
-      <c r="AV6" s="8" t="inlineStr"/>
-      <c r="AW6" s="8" t="inlineStr"/>
-      <c r="AX6" s="8" t="inlineStr"/>
-      <c r="AY6" s="8" t="inlineStr"/>
+      <c r="AU6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV6" s="8" t="n"/>
+      <c r="AW6" s="8" t="n">
+        <v>4325.11</v>
+      </c>
+      <c r="AX6" s="8" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="AY6" s="8" t="inlineStr">
+        <is>
+          <t>M1 4325.11</t>
+        </is>
+      </c>
       <c r="AZ6" s="8" t="inlineStr"/>
       <c r="BA6" s="8" t="inlineStr"/>
       <c r="BB6" s="8" t="inlineStr"/>
@@ -4058,10 +4082,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -4127,7 +4151,7 @@
         <v>2</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>-39.2</v>
+        <v>-12.66</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>46176.25</v>
@@ -4243,7 +4267,7 @@
         <v>6</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>2.23</v>
+        <v>28.77</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>46176.25</v>
@@ -4252,66 +4276,8 @@
         <v>46179.125</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>bt_s14_family</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>18.91</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>46176.25</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>46179.125</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>bt_s14_family</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>-16.68</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>46177.76041666666</v>
-      </c>
-      <c r="G8" s="11" t="n">
-        <v>46177.76041666666</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>